--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486700_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486700_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0043</v>
+        <v>2.2528</v>
       </c>
       <c r="E2" t="n">
-        <v>0.872</v>
+        <v>-0.0036</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1322</v>
+        <v>2.2564</v>
       </c>
       <c r="G2" t="n">
         <v>0.9103</v>
@@ -610,13 +610,13 @@
         <v>1.3515</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6341</v>
+        <v>-0.1173</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8544</v>
+        <v>-0.0212</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2203</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>0.1083</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2339</v>
+        <v>2.0244</v>
       </c>
       <c r="E3" t="n">
-        <v>1.9835</v>
+        <v>1.625</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2504</v>
+        <v>0.3994</v>
       </c>
       <c r="G3" t="n">
         <v>0.2114</v>
@@ -688,13 +688,13 @@
         <v>2.7031</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0665</v>
+        <v>-0.276</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6888</v>
+        <v>0.3303</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7552</v>
+        <v>-0.6062</v>
       </c>
       <c r="V3" t="n">
         <v>0.3513</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3066</v>
+        <v>0.039</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.6894</v>
+        <v>-2.6342</v>
       </c>
       <c r="F5" t="n">
-        <v>2.996</v>
+        <v>2.6732</v>
       </c>
       <c r="G5" t="n">
         <v>1.5566</v>
@@ -844,13 +844,13 @@
         <v>1.5446</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6012</v>
+        <v>-0.8689</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6349</v>
+        <v>-0.5797</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0336</v>
+        <v>-0.2892</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2626</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MOLINA MELENDEZ</t>
+          <t>P. JURAN HRVATSKO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2487</v>
+        <v>-0.3334</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4325</v>
+        <v>-0.642</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6812</v>
+        <v>0.3086</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1414</v>
+        <v>-1.0352</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.0613</v>
+        <v>-0.2553</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2028</v>
+        <v>-0.7799</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4878</v>
+        <v>-0.6281</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2327</v>
+        <v>0.0207</v>
       </c>
       <c r="L6" t="n">
-        <v>1.7205</v>
+        <v>-0.6488</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3464</v>
+        <v>-0.4071</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8286</v>
+        <v>-0.2759</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5178</v>
+        <v>-0.1311</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.1239</v>
+        <v>0.3862</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.8616</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7377</v>
+        <v>0.3862</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1198</v>
+        <v>-0.0552</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9647</v>
+        <v>-0.0139</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1552</v>
+        <v>-0.0413</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6138</v>
+        <v>0.3709</v>
       </c>
       <c r="W6" t="n">
-        <v>1.8415</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2277</v>
+        <v>0.3709</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. JURAN HRVATSKO</t>
+          <t>J. MOLINA MELENDEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6202</v>
+        <v>-0.7825</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.904</v>
+        <v>0.1222</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2838</v>
+        <v>-0.9046999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.0352</v>
+        <v>0.1414</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2553</v>
+        <v>-1.0613</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7799</v>
+        <v>1.2028</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.6281</v>
+        <v>1.4878</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0207</v>
+        <v>-0.2327</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6488</v>
+        <v>1.7205</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4071</v>
+        <v>-1.3464</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2759</v>
+        <v>-0.8286</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1311</v>
+        <v>-0.5178</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3862</v>
+        <v>-2.1239</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-3.8616</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3862</v>
+        <v>1.7377</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3421</v>
+        <v>0.5861</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2759</v>
+        <v>0.6544</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.06619999999999999</v>
+        <v>-0.0683</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3709</v>
+        <v>0.6138</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.8415</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3709</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1355</v>
+        <v>-1.7467</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.9371</v>
+        <v>-2.5234</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8016</v>
+        <v>0.7768</v>
       </c>
       <c r="G8" t="n">
         <v>-3.9177</v>
@@ -1078,13 +1078,13 @@
         <v>1.7377</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2372</v>
+        <v>0.1517</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1384</v>
+        <v>0.2753</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0988</v>
+        <v>-0.1236</v>
       </c>
       <c r="V8" t="n">
         <v>2.2124</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. HERNÁNDEZ TRUJILLO</t>
+          <t>A. PÉREZ PEREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4583</v>
+        <v>-1.8975</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.816</v>
+        <v>-0.8966</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6423</v>
+        <v>-1.001</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.6648</v>
+        <v>-2.009</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.8691</v>
+        <v>-0.4898</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7957</v>
+        <v>-1.5191</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.8983</v>
+        <v>-0.3184</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.9029</v>
+        <v>-0.2823</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0046</v>
+        <v>-0.0361</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7665</v>
+        <v>-1.6906</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9661999999999999</v>
+        <v>-0.2075</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8003</v>
+        <v>-1.483</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5446</v>
+        <v>1.9308</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5446</v>
+        <v>1.9308</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3807</v>
+        <v>-0.2208</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0824</v>
+        <v>-0.2073</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4631</v>
+        <v>-0.0135</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0426</v>
+        <v>-1.5985</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.3709</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0426</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. PÉREZ PEREZ</t>
+          <t>J. HERNÁNDEZ TRUJILLO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5926</v>
+        <v>-2.2018</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5171</v>
+        <v>-1.6091</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0755</v>
+        <v>-0.5927</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.009</v>
+        <v>-3.6648</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4898</v>
+        <v>-2.8691</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5191</v>
+        <v>-0.7957</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3184</v>
+        <v>-1.8983</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2823</v>
+        <v>-1.9029</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0361</v>
+        <v>0.0046</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6906</v>
+        <v>-1.7665</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2075</v>
+        <v>-0.9661999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.483</v>
+        <v>-0.8003</v>
       </c>
       <c r="P10" t="n">
-        <v>1.9308</v>
+        <v>1.5446</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9308</v>
+        <v>1.5446</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9157999999999999</v>
+        <v>-0.1242</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8279</v>
+        <v>0.2892</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.08799999999999999</v>
+        <v>-0.4134</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.5985</v>
+        <v>0.0426</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.3709</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2277</v>
+        <v>0.0426</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9976</v>
+        <v>-2.5866</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1202</v>
+        <v>-2.8582</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1225</v>
+        <v>0.2715</v>
       </c>
       <c r="G11" t="n">
         <v>-0.3075</v>
@@ -1312,13 +1312,13 @@
         <v>1.3515</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9489</v>
+        <v>-0.5379</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5245</v>
+        <v>-0.2625</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4244</v>
+        <v>-0.2754</v>
       </c>
       <c r="V11" t="n">
         <v>-1.162</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.9468</v>
+        <v>-4.670999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.944799999999999</v>
+        <v>-9.668900000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>4.9978</v>
+        <v>4.997800000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-7.343100000000001</v>
@@ -1360,7 +1360,7 @@
         <v>-7.2415</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1013000000000005</v>
+        <v>-0.1013000000000004</v>
       </c>
       <c r="J12" t="n">
         <v>-2.3674</v>
@@ -1375,13 +1375,13 @@
         <v>-4.9757</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.4889</v>
+        <v>-4.488899999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4865000000000005</v>
+        <v>-0.4865</v>
       </c>
       <c r="P12" t="n">
-        <v>3.861499999999999</v>
+        <v>3.8615</v>
       </c>
       <c r="Q12" t="n">
         <v>-10.6194</v>
@@ -1390,16 +1390,16 @@
         <v>14.4808</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.2074</v>
+        <v>-1.9314</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1423999999999997</v>
+        <v>0.1334999999999998</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.065</v>
+        <v>-2.0649</v>
       </c>
       <c r="V12" t="n">
-        <v>0.7418000000000005</v>
+        <v>0.7418000000000002</v>
       </c>
       <c r="W12" t="n">
         <v>3.1842</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L. NVE MALEVA</t>
+          <t>R. KOWALSKI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.7403</v>
+        <v>4.1566</v>
       </c>
       <c r="E13" t="n">
-        <v>3.733</v>
+        <v>2.6132</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0073</v>
+        <v>1.5434</v>
       </c>
       <c r="G13" t="n">
-        <v>4.3781</v>
+        <v>3.4361</v>
       </c>
       <c r="H13" t="n">
-        <v>3.9034</v>
+        <v>2.2559</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4747</v>
+        <v>1.1802</v>
       </c>
       <c r="J13" t="n">
-        <v>2.979</v>
+        <v>2.9206</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9383</v>
+        <v>2.0501</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0407</v>
+        <v>0.8706</v>
       </c>
       <c r="M13" t="n">
-        <v>1.3991</v>
+        <v>0.5154</v>
       </c>
       <c r="N13" t="n">
-        <v>0.9651</v>
+        <v>0.2058</v>
       </c>
       <c r="O13" t="n">
-        <v>0.434</v>
+        <v>0.3096</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9308</v>
+        <v>-3.0892</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9654</v>
+        <v>1.1585</v>
       </c>
       <c r="S13" t="n">
-        <v>2.4548</v>
+        <v>0.5241</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3992</v>
+        <v>0.0408</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0556</v>
+        <v>0.4833</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.1271</v>
+        <v>2.1271</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2856</v>
+        <v>2.741</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.4128</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. KOWALSKI</t>
+          <t>L. NVE MALEVA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.6877</v>
+        <v>2.3406</v>
       </c>
       <c r="E14" t="n">
-        <v>2.4064</v>
+        <v>2.1817</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2813</v>
+        <v>0.159</v>
       </c>
       <c r="G14" t="n">
-        <v>3.4361</v>
+        <v>4.3781</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2559</v>
+        <v>3.9034</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1802</v>
+        <v>0.4747</v>
       </c>
       <c r="J14" t="n">
-        <v>2.9206</v>
+        <v>2.979</v>
       </c>
       <c r="K14" t="n">
-        <v>2.0501</v>
+        <v>2.9383</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8706</v>
+        <v>0.0407</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5154</v>
+        <v>1.3991</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2058</v>
+        <v>0.9651</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3096</v>
+        <v>0.434</v>
       </c>
       <c r="P14" t="n">
+        <v>-0.9654</v>
+      </c>
+      <c r="Q14" t="n">
         <v>-1.9308</v>
       </c>
-      <c r="Q14" t="n">
-        <v>-3.0892</v>
-      </c>
       <c r="R14" t="n">
-        <v>1.1585</v>
+        <v>0.9654</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0552</v>
+        <v>1.0551</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.166</v>
+        <v>0.8478</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2213</v>
+        <v>0.2072</v>
       </c>
       <c r="V14" t="n">
-        <v>2.1271</v>
+        <v>-2.1271</v>
       </c>
       <c r="W14" t="n">
-        <v>2.741</v>
+        <v>0.2856</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6138</v>
+        <v>-2.4128</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1712</v>
+        <v>1.2416</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0275</v>
+        <v>-0.593</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1437</v>
+        <v>1.8346</v>
       </c>
       <c r="G15" t="n">
         <v>1.2827</v>
@@ -1624,13 +1624,13 @@
         <v>1.5446</v>
       </c>
       <c r="S15" t="n">
-        <v>1.8812</v>
+        <v>0.9516</v>
       </c>
       <c r="T15" t="n">
-        <v>1.075</v>
+        <v>0.4545</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8061</v>
+        <v>0.4971</v>
       </c>
       <c r="V15" t="n">
         <v>-0.4135</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.836</v>
+        <v>0.7822</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2062</v>
+        <v>0.1027</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6298</v>
+        <v>0.6795</v>
       </c>
       <c r="G16" t="n">
         <v>0.261</v>
@@ -1702,13 +1702,13 @@
         <v>0.1931</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6675</v>
+        <v>0.6138</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4411</v>
+        <v>0.3377</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2264</v>
+        <v>0.2761</v>
       </c>
       <c r="V16" t="n">
         <v>-0.2856</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. KALINICENKO</t>
+          <t>C. TEASLEY JR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2624</v>
+        <v>0.5312</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1937</v>
+        <v>-0.2163</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4561</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0471</v>
+        <v>0.6236</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1308</v>
+        <v>1.3448</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0837</v>
+        <v>-0.7212</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5867</v>
+        <v>2.0805</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0621</v>
+        <v>1.3458</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6488</v>
+        <v>0.7347</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6338</v>
+        <v>-1.4569</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0687</v>
+        <v>-0.0009</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5651</v>
+        <v>-1.456</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.5792</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9654</v>
+        <v>-2.1239</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3862</v>
+        <v>1.9308</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7945</v>
+        <v>-0.2276</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3584</v>
+        <v>-0.173</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4361</v>
+        <v>-0.0546</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.3282</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>0.3282</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. PUJADAS TARRADELLAS</t>
+          <t>A. KALINICENKO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9429999999999999</v>
+        <v>0.1093</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.2393</v>
+        <v>-1.2971</v>
       </c>
       <c r="F18" t="n">
-        <v>3.2963</v>
+        <v>1.4064</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.88</v>
+        <v>0.0471</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0278</v>
+        <v>0.1308</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8522</v>
+        <v>-0.0837</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.6159</v>
+        <v>-0.5867</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.8542</v>
+        <v>0.0621</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.7617</v>
+        <v>-0.6488</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7359</v>
+        <v>0.6338</v>
       </c>
       <c r="N18" t="n">
-        <v>0.8264</v>
+        <v>0.0687</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0905</v>
+        <v>0.5651</v>
       </c>
       <c r="P18" t="n">
+        <v>-0.5792</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-0.9654</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.3862</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.6414</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.3865</v>
+      </c>
+      <c r="V18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-2.1239</v>
-      </c>
-      <c r="R18" t="n">
-        <v>2.1239</v>
-      </c>
-      <c r="S18" t="n">
-        <v>-0.6342</v>
-      </c>
-      <c r="T18" t="n">
-        <v>-0.4143</v>
-      </c>
-      <c r="U18" t="n">
-        <v>-0.2199</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0.5712</v>
-      </c>
       <c r="W18" t="n">
-        <v>-0.0852</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.6565</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. TEASLEY JR</t>
+          <t>A. PUJADAS TARRADELLAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0231</v>
+        <v>-0.1501</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1471</v>
+        <v>-3.7222</v>
       </c>
       <c r="F19" t="n">
-        <v>0.124</v>
+        <v>3.5721</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6236</v>
+        <v>-0.88</v>
       </c>
       <c r="H19" t="n">
-        <v>1.3448</v>
+        <v>-0.0278</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7212</v>
+        <v>-0.8522</v>
       </c>
       <c r="J19" t="n">
-        <v>2.0805</v>
+        <v>-1.6159</v>
       </c>
       <c r="K19" t="n">
-        <v>1.3458</v>
+        <v>-0.8542</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7347</v>
+        <v>-0.7617</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4569</v>
+        <v>0.7359</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0009</v>
+        <v>0.8264</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.456</v>
+        <v>-0.0905</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1931</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>-2.1239</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9308</v>
+        <v>2.1239</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.7818</v>
+        <v>0.1587</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1038</v>
+        <v>0.1028</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6781</v>
+        <v>0.0559</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3282</v>
+        <v>0.5712</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.0852</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3282</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0275</v>
+        <v>-0.6897</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.9919</v>
+        <v>-2.6816</v>
       </c>
       <c r="F20" t="n">
-        <v>1.9644</v>
+        <v>1.9919</v>
       </c>
       <c r="G20" t="n">
         <v>-2.0678</v>
@@ -2014,13 +2014,13 @@
         <v>1.7377</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1101</v>
+        <v>0.2276</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2211</v>
+        <v>0.0892</v>
       </c>
       <c r="U20" t="n">
-        <v>0.111</v>
+        <v>0.1384</v>
       </c>
       <c r="V20" t="n">
         <v>0.5712</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1571</v>
+        <v>-0.9792</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9831</v>
+        <v>-0.8797</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.174</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="G21" t="n">
         <v>0.2648</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1709</v>
+        <v>0.007</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>0.1034</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1709</v>
+        <v>-0.0965</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2856</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5999</v>
+        <v>-1.0165</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8156</v>
+        <v>-0.5054</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7843</v>
+        <v>-0.5112</v>
       </c>
       <c r="G22" t="n">
         <v>-0.0027</v>
@@ -2170,13 +2170,13 @@
         <v>0.5792</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9488</v>
+        <v>-0.3654</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3037</v>
+        <v>0.0066</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6452</v>
+        <v>-0.372</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2277</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>4.947</v>
+        <v>6.326000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.997599999999999</v>
+        <v>-4.997699999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>9.944599999999999</v>
+        <v>11.3237</v>
       </c>
       <c r="G23" t="n">
         <v>7.342899999999999</v>
@@ -2248,13 +2248,13 @@
         <v>10.6194</v>
       </c>
       <c r="S23" t="n">
-        <v>2.2074</v>
+        <v>3.5863</v>
       </c>
       <c r="T23" t="n">
         <v>2.0648</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1423999999999999</v>
+        <v>1.5214</v>
       </c>
       <c r="V23" t="n">
         <v>-0.7418</v>
